--- a/data/trans_orig/IQ23_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>35745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54955</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>71829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86876</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64600</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79145</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141944</t>
+          <t>141551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161931</t>
+          <t>160974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26339</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51975</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>57489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71121</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>54739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68234</t>
+          <t>68031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116760</t>
+          <t>117616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135568</t>
+          <t>135422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33223</t>
+          <t>33255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51368</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40610</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>111551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129781</t>
+          <t>129768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64358</t>
+          <t>63975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37048</t>
+          <t>38005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85717</t>
+          <t>86100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113431</t>
+          <t>114025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>131168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151578</t>
+          <t>151797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142095</t>
+          <t>142405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162203</t>
+          <t>160850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>280199</t>
+          <t>278707</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>308500</t>
+          <t>308361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66462</t>
+          <t>65259</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66823</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80915</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156785</t>
+          <t>158071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>179359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27448</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64078</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44387</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>100238</t>
+          <t>100731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>118057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>31891</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>137177</t>
+          <t>139156</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171839</t>
+          <t>173351</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>145428</t>
+          <t>147290</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>180967</t>
+          <t>183083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>295559</t>
+          <t>294659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>344595</t>
+          <t>342365</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450372</t>
+          <t>449371</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>485710</t>
+          <t>482974</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>486578</t>
+          <t>484223</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>523604</t>
+          <t>521804</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>946327</t>
+          <t>948784</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>996460</t>
+          <t>997198</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>54341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62894</t>
+          <t>63458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76033</t>
+          <t>76431</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52907</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122661</t>
+          <t>121236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140332</t>
+          <t>140059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50878</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63378</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76850</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>64950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133044</t>
+          <t>133947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152756</t>
+          <t>153561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>52332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66051</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>55115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>68794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112364</t>
+          <t>113887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132248</t>
+          <t>132625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70758</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>72068</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102808</t>
+          <t>105912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134829</t>
+          <t>135332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130035</t>
+          <t>129905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151482</t>
+          <t>151361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147287</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171914</t>
+          <t>170976</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>284572</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>316139</t>
+          <t>315614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45599</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>51697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64849</t>
+          <t>65954</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>90673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>96797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115484</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101715</t>
+          <t>102462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>187659</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212802</t>
+          <t>212045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33404</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65579</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92226</t>
+          <t>92185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106883</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>29485</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>153061</t>
+          <t>154455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>190082</t>
+          <t>190509</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>163174</t>
+          <t>164319</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>204128</t>
+          <t>203072</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>328588</t>
+          <t>327066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>382595</t>
+          <t>380416</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>470260</t>
+          <t>468351</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>507746</t>
+          <t>506280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>491903</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>533598</t>
+          <t>530364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>973533</t>
+          <t>973260</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1026898</t>
+          <t>1027512</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>39788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38396</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53170</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>73761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74586</t>
+          <t>74977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103414</t>
+          <t>104171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124282</t>
+          <t>125333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>50597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71472</t>
+          <t>70977</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69915</t>
+          <t>70454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84185</t>
+          <t>84081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65257</t>
+          <t>65273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>81439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>139886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160634</t>
+          <t>161305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32303</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>47229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>44006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83862</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57799</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80163</t>
+          <t>79603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60997</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126790</t>
+          <t>126784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157524</t>
+          <t>158138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135670</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158607</t>
+          <t>158705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121873</t>
+          <t>122002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144844</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264364</t>
+          <t>263283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295572</t>
+          <t>295149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>42679</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66766</t>
+          <t>67779</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92278</t>
+          <t>91415</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91221</t>
+          <t>90509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107372</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87845</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106149</t>
+          <t>107601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183449</t>
+          <t>184369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209062</t>
+          <t>208018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46278</t>
+          <t>46818</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49673</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78250</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95412</t>
+          <t>95423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179228</t>
+          <t>177754</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>218001</t>
+          <t>216656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>203887</t>
+          <t>206827</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>245818</t>
+          <t>247017</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>396653</t>
+          <t>392512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>453734</t>
+          <t>452084</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>435548</t>
+          <t>438022</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>476522</t>
+          <t>477963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>445535</t>
+          <t>444923</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>487235</t>
+          <t>485087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>890706</t>
+          <t>894230</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>951022</t>
+          <t>953874</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>74498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80367</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>90936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110957</t>
+          <t>109908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>162914</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>186526</t>
+          <t>186174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56709</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60502</t>
+          <t>59641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74599</t>
+          <t>73910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65962</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>79715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130072</t>
+          <t>128948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>150165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>45287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32119</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35540</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49132</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88883</t>
+          <t>88708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74029</t>
+          <t>73854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>59260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87924</t>
+          <t>86222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104782</t>
+          <t>105995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152322</t>
+          <t>154359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>138432</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>176176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127373</t>
+          <t>128429</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>274330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324848</t>
+          <t>324000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>65178</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96209</t>
+          <t>95871</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102272</t>
+          <t>103364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126619</t>
+          <t>127696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181298</t>
+          <t>181015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210067</t>
+          <t>211730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>29789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47914</t>
+          <t>47901</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54847</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88794</t>
+          <t>88296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>106454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,77 +13762,77 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>16967</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>16845</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10414</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>26476</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>8017</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>3652</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>16714</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>16845</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>10044</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151383</t>
+          <t>151034</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>200825</t>
+          <t>199097</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193691</t>
+          <t>193224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>241620</t>
+          <t>240701</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>363001</t>
+          <t>355585</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>429786</t>
+          <t>426361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>441280</t>
+          <t>443270</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>492589</t>
+          <t>493592</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>497648</t>
+          <t>498408</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>545864</t>
+          <t>545413</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>951507</t>
+          <t>955336</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1019196</t>
+          <t>1026684</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Clase-trans_orig.xlsx
@@ -726,213 +726,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3222</v>
+        <v>21571</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1238</v>
+        <v>15128</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7680</v>
+        <v>28281</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03302773637415684</v>
+        <v>0.2211435407511494</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.01269604370779296</v>
+        <v>0.155083349390694</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.07873333780840711</v>
+        <v>0.2899318598060276</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>901</v>
+        <v>23465</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>17035</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>3173</v>
+        <v>31002</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.008675379976796153</v>
+        <v>0.2258360540285567</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>0.1639532893138767</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.03053855993060195</v>
+        <v>0.2983762632228293</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>4123</v>
+        <v>45037</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>1798</v>
+        <v>36111</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>8894</v>
+        <v>54365</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.020467200444799</v>
+        <v>0.2235638601920332</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.00892728241438763</v>
+        <v>0.1792536444758384</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.0441496809503155</v>
+        <v>0.2698699486922429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>21571</v>
+        <v>72752</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>15128</v>
+        <v>65451</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>28281</v>
+        <v>79314</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2211435407511494</v>
+        <v>0.7458287228746938</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.155083349390694</v>
+        <v>0.67098709652989</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2899318598060276</v>
+        <v>0.8131046924428209</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>23465</v>
+        <v>79537</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>17035</v>
+        <v>72297</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>31002</v>
+        <v>86188</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2258360540285567</v>
+        <v>0.7654885659946472</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.1639532893138767</v>
+        <v>0.6958054701634739</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2983762632228293</v>
+        <v>0.8294961177750809</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>45037</v>
+        <v>152290</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>36111</v>
+        <v>142527</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>54365</v>
+        <v>161749</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2235638601920332</v>
+        <v>0.7559689393631678</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.1792536444758384</v>
+        <v>0.7075054514382063</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2698699486922429</v>
+        <v>0.8029216007680087</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>72752</v>
+        <v>3222</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>65451</v>
+        <v>1238</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>79314</v>
+        <v>7680</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7458287228746938</v>
+        <v>0.03302773637415684</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.67098709652989</v>
+        <v>0.01269604370779296</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.8131046924428209</v>
+        <v>0.07873333780840711</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>79537</v>
+        <v>901</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>72297</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>86188</v>
+        <v>3173</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7654885659946472</v>
+        <v>0.008675379976796153</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6958054701634739</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.8294961177750809</v>
+        <v>0.03053855993060195</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>152290</v>
+        <v>4123</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>142527</v>
+        <v>1798</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>161749</v>
+        <v>8894</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7559689393631678</v>
+        <v>0.020467200444799</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.7075054514382063</v>
+        <v>0.00892728241438763</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.8029216007680087</v>
+        <v>0.0441496809503155</v>
       </c>
     </row>
     <row r="7">
@@ -1014,213 +1014,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>647</v>
+        <v>22535</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>16417</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3249</v>
+        <v>29622</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.007634272833662293</v>
+        <v>0.2657639968258282</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>0.1936119500280712</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03832021073755474</v>
+        <v>0.3493484603852141</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1818</v>
+        <v>19771</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>521</v>
+        <v>14628</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>5047</v>
+        <v>26670</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02099158461747417</v>
+        <v>0.2282532182000687</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.0060182697349209</v>
+        <v>0.1688745520550838</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.05826684579447022</v>
+        <v>0.3078924492406492</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>2466</v>
+        <v>42306</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>647</v>
+        <v>34453</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>5759</v>
+        <v>51448</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01438415028753244</v>
+        <v>0.2468085989867225</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.003773763690496905</v>
+        <v>0.200994387055707</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.03359880170084663</v>
+        <v>0.3001451130938678</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>22535</v>
+        <v>61610</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>16417</v>
+        <v>54207</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>29622</v>
+        <v>67527</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2657639968258282</v>
+        <v>0.7266017303405096</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1936119500280712</v>
+        <v>0.6392903549206856</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3493484603852141</v>
+        <v>0.7963816723749715</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>19771</v>
+        <v>65030</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>14628</v>
+        <v>58461</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>26670</v>
+        <v>70791</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2282532182000687</v>
+        <v>0.7507551971824571</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1688745520550838</v>
+        <v>0.6749133013222626</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3078924492406492</v>
+        <v>0.8172566243963396</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>42306</v>
+        <v>126640</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>34453</v>
+        <v>117098</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>51448</v>
+        <v>134969</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2468085989867225</v>
+        <v>0.738807250725745</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.200994387055707</v>
+        <v>0.6831390595870497</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3001451130938678</v>
+        <v>0.78739391015083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>61610</v>
+        <v>647</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>54207</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>67527</v>
+        <v>3249</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7266017303405096</v>
+        <v>0.007634272833662293</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6392903549206856</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7963816723749715</v>
+        <v>0.03832021073755474</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>65030</v>
+        <v>1818</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>58461</v>
+        <v>521</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>70791</v>
+        <v>5047</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7507551971824571</v>
+        <v>0.02099158461747417</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6749133013222626</v>
+        <v>0.0060182697349209</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.8172566243963396</v>
+        <v>0.05826684579447022</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>126640</v>
+        <v>2466</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>117098</v>
+        <v>647</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>134969</v>
+        <v>5759</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.738807250725745</v>
+        <v>0.01438415028753244</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6831390595870497</v>
+        <v>0.003773763690496905</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.78739391015083</v>
+        <v>0.03359880170084663</v>
       </c>
     </row>
     <row r="11">
@@ -1302,213 +1302,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>686</v>
+        <v>24396</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>17943</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3318</v>
+        <v>31375</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.006955544182890398</v>
+        <v>0.2473063315744691</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.1818989610067532</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03364002023525928</v>
+        <v>0.3180605243847207</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2814</v>
+        <v>17426</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>778</v>
+        <v>11823</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>6916</v>
+        <v>23798</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.04175748901355526</v>
+        <v>0.2585809258220081</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.01154761233806477</v>
+        <v>0.1754363480975798</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1026285902396244</v>
+        <v>0.3531330192251571</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>3500</v>
+        <v>41822</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>1307</v>
+        <v>33319</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>7659</v>
+        <v>51059</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02108111029026354</v>
+        <v>0.2518825133698351</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.00787206659282977</v>
+        <v>0.2006717694436819</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.04612746454953694</v>
+        <v>0.3075136600151339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>24396</v>
+        <v>73563</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>17943</v>
+        <v>66786</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>31375</v>
+        <v>80105</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2473063315744691</v>
+        <v>0.7457381242426404</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1818989610067532</v>
+        <v>0.6770311858398401</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3180605243847207</v>
+        <v>0.8120566288986938</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>17426</v>
+        <v>47152</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>11823</v>
+        <v>40760</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>23798</v>
+        <v>52857</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2585809258220081</v>
+        <v>0.6996615851644367</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1754363480975798</v>
+        <v>0.6048158553227697</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3531330192251571</v>
+        <v>0.784326560373809</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>41822</v>
+        <v>120716</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>33319</v>
+        <v>111041</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>51059</v>
+        <v>129039</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2518825133698351</v>
+        <v>0.7270363763399014</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2006717694436819</v>
+        <v>0.6687692832046059</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3075136600151339</v>
+        <v>0.7771640287694063</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>73563</v>
+        <v>686</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>66786</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>80105</v>
+        <v>3318</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7457381242426404</v>
+        <v>0.006955544182890398</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6770311858398401</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8120566288986938</v>
+        <v>0.03364002023525928</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>47152</v>
+        <v>2814</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>40760</v>
+        <v>778</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>52857</v>
+        <v>6916</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6996615851644367</v>
+        <v>0.04175748901355526</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6048158553227697</v>
+        <v>0.01154761233806477</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.784326560373809</v>
+        <v>0.1026285902396244</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>120716</v>
+        <v>3500</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>111041</v>
+        <v>1307</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>129039</v>
+        <v>7659</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7270363763399014</v>
+        <v>0.02108111029026354</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6687692832046059</v>
+        <v>0.00787206659282977</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7771640287694063</v>
+        <v>0.04612746454953694</v>
       </c>
     </row>
     <row r="15">
@@ -1590,213 +1590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3431</v>
+        <v>46552</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1296</v>
+        <v>37795</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7033</v>
+        <v>56685</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01697851096961875</v>
+        <v>0.2303692498794667</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.006412544983926776</v>
+        <v>0.1870341946738583</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03480468372597182</v>
+        <v>0.280515888145829</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2631</v>
+        <v>53377</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>630</v>
+        <v>43883</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>6346</v>
+        <v>63752</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01329296292823641</v>
+        <v>0.2696933053403421</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.00318559359620162</v>
+        <v>0.2217237730719256</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03206135537713243</v>
+        <v>0.3221150104456454</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>6062</v>
+        <v>99929</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>2683</v>
+        <v>86384</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>11053</v>
+        <v>113980</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01515488515480721</v>
+        <v>0.2498269701089488</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.00670843657641395</v>
+        <v>0.2159651757579458</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.02763382880370986</v>
+        <v>0.2849547044607058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>46552</v>
+        <v>152091</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>37795</v>
+        <v>142091</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>56685</v>
+        <v>160941</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2303692498794667</v>
+        <v>0.7526522391509145</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1870341946738583</v>
+        <v>0.7031627768680898</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.280515888145829</v>
+        <v>0.7964481694034646</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>53377</v>
+        <v>141910</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>43883</v>
+        <v>130914</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>63752</v>
+        <v>151455</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2696933053403421</v>
+        <v>0.7170137317314215</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2217237730719256</v>
+        <v>0.6614550650799207</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3221150104456454</v>
+        <v>0.765239282211245</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>154</v>
+        <v>440</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>99929</v>
+        <v>294001</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>86384</v>
+        <v>279028</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>113980</v>
+        <v>308210</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2498269701089488</v>
+        <v>0.7350181447362439</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2159651757579458</v>
+        <v>0.6975842222670599</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2849547044607058</v>
+        <v>0.7705403055614234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>227</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>152091</v>
+        <v>3431</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>142091</v>
+        <v>1296</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>160941</v>
+        <v>7033</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7526522391509145</v>
+        <v>0.01697851096961875</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7031627768680898</v>
+        <v>0.006412544983926776</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7964481694034646</v>
+        <v>0.03480468372597182</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>141910</v>
+        <v>2631</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>130914</v>
+        <v>630</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>151455</v>
+        <v>6346</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7170137317314215</v>
+        <v>0.01329296292823641</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6614550650799207</v>
+        <v>0.00318559359620162</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.765239282211245</v>
+        <v>0.03206135537713243</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>440</v>
+        <v>9</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>294001</v>
+        <v>6062</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>279028</v>
+        <v>2683</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>308210</v>
+        <v>11053</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7350181447362439</v>
+        <v>0.01515488515480721</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6975842222670599</v>
+        <v>0.00670843657641395</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7705403055614234</v>
+        <v>0.02763382880370986</v>
       </c>
     </row>
     <row r="19">
@@ -1878,213 +1878,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>3966</v>
+        <v>27279</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1787</v>
+        <v>20615</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>8104</v>
+        <v>34523</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.03148943526661065</v>
+        <v>0.2166136104177285</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01418808651187283</v>
+        <v>0.1636958116453384</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.06435572325678827</v>
+        <v>0.2741404877510911</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1730</v>
+        <v>27402</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>519</v>
+        <v>20404</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4758</v>
+        <v>34984</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01671706893491984</v>
+        <v>0.2647479637482485</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.005018371278458085</v>
+        <v>0.1971336313235751</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.04597300683520648</v>
+        <v>0.3380008171104407</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>5696</v>
+        <v>54681</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>2599</v>
+        <v>46018</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>9985</v>
+        <v>66567</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02482529174566838</v>
+        <v>0.2383280894443</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01132874896443688</v>
+        <v>0.2005686129794046</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.04352098735147805</v>
+        <v>0.2901353522548779</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>27279</v>
+        <v>94688</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>20615</v>
+        <v>86922</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>34523</v>
+        <v>101530</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2166136104177285</v>
+        <v>0.7518969543156608</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1636958116453384</v>
+        <v>0.6902307287688549</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2741404877510911</v>
+        <v>0.8062269877805218</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>27402</v>
+        <v>74371</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>20404</v>
+        <v>66986</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>34984</v>
+        <v>81449</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2647479637482485</v>
+        <v>0.7185349673168316</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1971336313235751</v>
+        <v>0.6471857143136405</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3380008171104407</v>
+        <v>0.7869118674454483</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>54681</v>
+        <v>169059</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>46018</v>
+        <v>157059</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>66567</v>
+        <v>177834</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2383280894443</v>
+        <v>0.7368466188100317</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2005686129794046</v>
+        <v>0.6845438360861216</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2901353522548779</v>
+        <v>0.7750941291033411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>94688</v>
+        <v>3966</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>86922</v>
+        <v>1787</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>101530</v>
+        <v>8104</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7518969543156608</v>
+        <v>0.03148943526661065</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6902307287688549</v>
+        <v>0.01418808651187283</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.8062269877805218</v>
+        <v>0.06435572325678827</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>74371</v>
+        <v>1730</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>66986</v>
+        <v>519</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>81449</v>
+        <v>4758</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7185349673168316</v>
+        <v>0.01671706893491984</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6471857143136405</v>
+        <v>0.005018371278458085</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7869118674454483</v>
+        <v>0.04597300683520648</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>169059</v>
+        <v>5696</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>157059</v>
+        <v>2599</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>177834</v>
+        <v>9985</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7368466188100317</v>
+        <v>0.02482529174566838</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6845438360861216</v>
+        <v>0.01132874896443688</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7750941291033411</v>
+        <v>0.04352098735147805</v>
       </c>
     </row>
     <row r="23">
@@ -2166,213 +2166,213 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>648</v>
+        <v>21092</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>15628</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>3691</v>
+        <v>28139</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.008955850354176531</v>
+        <v>0.2913599567717123</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>0.2158838192885202</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.05098410995136352</v>
+        <v>0.3887029319472853</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>1252</v>
+        <v>14164</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>9475</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>4441</v>
+        <v>20852</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.01690152465036759</v>
+        <v>0.1911491283503046</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>0.1278654728037676</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.05992987021736472</v>
+        <v>0.2814031308381384</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>1901</v>
+        <v>35257</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>618</v>
+        <v>27382</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>4936</v>
+        <v>43327</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.01297500775429579</v>
+        <v>0.2406703516346058</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.004215926456174038</v>
+        <v>0.1869144238334862</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.03369336835859511</v>
+        <v>0.295759726388779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>21092</v>
+        <v>50652</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>15628</v>
+        <v>43615</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>28139</v>
+        <v>56167</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.2913599567717123</v>
+        <v>0.6996841928741112</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.2158838192885202</v>
+        <v>0.6024888103473339</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.3887029319472853</v>
+        <v>0.7758661492597752</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>14164</v>
+        <v>58683</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>9475</v>
+        <v>52283</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>20852</v>
+        <v>63835</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1911491283503046</v>
+        <v>0.7919493469993278</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1278654728037676</v>
+        <v>0.7055679792582247</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2814031308381384</v>
+        <v>0.8614714646709707</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>35257</v>
+        <v>109336</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>27382</v>
+        <v>101539</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>43327</v>
+        <v>117445</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.2406703516346058</v>
+        <v>0.7463546406110985</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.1869144238334862</v>
+        <v>0.6931351156982186</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.295759726388779</v>
+        <v>0.8017106564821824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>50652</v>
+        <v>648</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>43615</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>56167</v>
+        <v>3691</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.6996841928741112</v>
+        <v>0.008955850354176531</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.6024888103473339</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.7758661492597752</v>
+        <v>0.05098410995136352</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>58683</v>
+        <v>1252</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>52283</v>
+        <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>63835</v>
+        <v>4441</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.7919493469993278</v>
+        <v>0.01690152465036759</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.7055679792582247</v>
+        <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8614714646709707</v>
+        <v>0.05992987021736472</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>109336</v>
+        <v>1901</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>101539</v>
+        <v>618</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>117445</v>
+        <v>4936</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.7463546406110985</v>
+        <v>0.01297500775429579</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.6931351156982186</v>
+        <v>0.004215926456174038</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.8017106564821824</v>
+        <v>0.03369336835859511</v>
       </c>
     </row>
     <row r="27">
@@ -2454,213 +2454,213 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>12600</v>
+        <v>163424</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>7856</v>
+        <v>144505</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>19283</v>
+        <v>181328</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01849176944887601</v>
+        <v>0.2398426662373746</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.01152931312050822</v>
+        <v>0.2120762602984908</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.02829963366762407</v>
+        <v>0.2661174043490594</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>11147</v>
+        <v>155607</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>6825</v>
+        <v>139199</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>17008</v>
+        <v>171784</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.0175982811699373</v>
+        <v>0.245654028411857</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.0107741755948182</v>
+        <v>0.2197508143453487</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.02685071685182933</v>
+        <v>0.2711937089775635</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>37</v>
+        <v>484</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>23747</v>
+        <v>319031</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>16928</v>
+        <v>296280</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>32392</v>
+        <v>343069</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.0180613153217437</v>
+        <v>0.2426423949984927</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.01287442756552305</v>
+        <v>0.225338599629971</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.02463633749754554</v>
+        <v>0.2609244250596098</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>248</v>
+        <v>757</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>163424</v>
+        <v>505358</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>144505</v>
+        <v>487777</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>181328</v>
+        <v>525687</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.2398426662373746</v>
+        <v>0.7416655643137494</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.2120762602984908</v>
+        <v>0.7158637204238492</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.2661174043490594</v>
+        <v>0.7715014402088138</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>236</v>
+        <v>691</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>155607</v>
+        <v>466684</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>139199</v>
+        <v>448196</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>171784</v>
+        <v>483652</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.245654028411857</v>
+        <v>0.7367476904182056</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2197508143453487</v>
+        <v>0.7075606866248417</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2711937089775635</v>
+        <v>0.7635346231166453</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>484</v>
+        <v>1448</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>319031</v>
+        <v>972042</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>296280</v>
+        <v>947021</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>343069</v>
+        <v>996256</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.2426423949984927</v>
+        <v>0.7392962896797637</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.225338599629971</v>
+        <v>0.7202664416737492</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.2609244250596098</v>
+        <v>0.7577126887528977</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>757</v>
+        <v>19</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>505358</v>
+        <v>12600</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>487777</v>
+        <v>7856</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>525687</v>
+        <v>19283</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.7416655643137494</v>
+        <v>0.01849176944887601</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.7158637204238492</v>
+        <v>0.01152931312050822</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.7715014402088138</v>
+        <v>0.02829963366762407</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>691</v>
+        <v>18</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>466684</v>
+        <v>11147</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>448196</v>
+        <v>6825</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>483652</v>
+        <v>17008</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7367476904182056</v>
+        <v>0.0175982811699373</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7075606866248417</v>
+        <v>0.0107741755948182</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.7635346231166453</v>
+        <v>0.02685071685182933</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1448</v>
+        <v>37</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>972042</v>
+        <v>23747</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>947021</v>
+        <v>16928</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>996256</v>
+        <v>32392</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.7392962896797637</v>
+        <v>0.0180613153217437</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.7202664416737492</v>
+        <v>0.01287442756552305</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.7577126887528977</v>
+        <v>0.02463633749754554</v>
       </c>
     </row>
     <row r="31">
@@ -2976,213 +2976,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1992</v>
+        <v>26666</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>638</v>
+        <v>19856</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>5238</v>
+        <v>34819</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.02218721211398256</v>
+        <v>0.2970699629667195</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.007104410670426261</v>
+        <v>0.2212083941671097</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.05835727554120893</v>
+        <v>0.3879043443442372</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1425</v>
+        <v>18089</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>12444</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>5439</v>
+        <v>24252</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.01584940562397676</v>
+        <v>0.2011348870922263</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>0.1383688028700317</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.06048014287303751</v>
+        <v>0.2696633185606551</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>3417</v>
+        <v>44755</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>1299</v>
+        <v>35882</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>7527</v>
+        <v>54690</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01901531154510246</v>
+        <v>0.2490570546802782</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.007229555990872914</v>
+        <v>0.1996782451582088</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.0418893354525217</v>
+        <v>0.3043477754093731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26666</v>
+        <v>61106</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>19856</v>
+        <v>52827</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>34819</v>
+        <v>68103</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2970699629667195</v>
+        <v>0.6807428249192979</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2212083941671097</v>
+        <v>0.5885157484789337</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3879043443442372</v>
+        <v>0.758702906623677</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>18089</v>
+        <v>70419</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12444</v>
+        <v>63727</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>24252</v>
+        <v>76008</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2011348870922263</v>
+        <v>0.783015707283797</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.1383688028700317</v>
+        <v>0.7086066005166989</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2696633185606551</v>
+        <v>0.8451613241795289</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>44755</v>
+        <v>131525</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>35882</v>
+        <v>121903</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>54690</v>
+        <v>140130</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2490570546802782</v>
+        <v>0.7319276337746193</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.1996782451582088</v>
+        <v>0.6783792771622871</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3043477754093731</v>
+        <v>0.7798147526085604</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>61106</v>
+        <v>1992</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>52827</v>
+        <v>638</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>68103</v>
+        <v>5238</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6807428249192979</v>
+        <v>0.02218721211398256</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5885157484789337</v>
+        <v>0.007104410670426261</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.758702906623677</v>
+        <v>0.05835727554120893</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>70419</v>
+        <v>1425</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>63727</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>76008</v>
+        <v>5439</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.783015707283797</v>
+        <v>0.01584940562397676</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.7086066005166989</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.8451613241795289</v>
+        <v>0.06048014287303751</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>189</v>
+        <v>5</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>131525</v>
+        <v>3417</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>121903</v>
+        <v>1299</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>140130</v>
+        <v>7527</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7319276337746193</v>
+        <v>0.01901531154510246</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6783792771622871</v>
+        <v>0.007229555990872914</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7798147526085604</v>
+        <v>0.0418893354525217</v>
       </c>
     </row>
     <row r="7">
@@ -3264,213 +3264,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2024</v>
+        <v>21821</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>638</v>
+        <v>15679</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5478</v>
+        <v>29066</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02091473841982325</v>
+        <v>0.2254753916684886</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.00659377791370222</v>
+        <v>0.162008626726272</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05659918362422012</v>
+        <v>0.3003348123686805</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>3356</v>
+        <v>19404</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1306</v>
+        <v>13161</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7424</v>
+        <v>26380</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.03598653398408653</v>
+        <v>0.2080456446680478</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01400199825949694</v>
+        <v>0.141116212945572</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.07959805769193443</v>
+        <v>0.2828445134180335</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>5380</v>
+        <v>41225</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>2653</v>
+        <v>32891</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>10624</v>
+        <v>50447</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02831134676461657</v>
+        <v>0.2169215991517707</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01395873478471465</v>
+        <v>0.1730707779208811</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.05590243579599176</v>
+        <v>0.2654513462694137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>21821</v>
+        <v>72933</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>15679</v>
+        <v>64986</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>29066</v>
+        <v>79119</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2254753916684886</v>
+        <v>0.7536098699116881</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.162008626726272</v>
+        <v>0.6714995630281011</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3003348123686805</v>
+        <v>0.8175339467336639</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>19404</v>
+        <v>70506</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>13161</v>
+        <v>63025</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>26380</v>
+        <v>76937</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2080456446680478</v>
+        <v>0.7559678213478657</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.141116212945572</v>
+        <v>0.6757515495440841</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2828445134180335</v>
+        <v>0.8249244920415855</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>41225</v>
+        <v>143439</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>32891</v>
+        <v>134103</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>50447</v>
+        <v>152498</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2169215991517707</v>
+        <v>0.7547670540836127</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.1730707779208811</v>
+        <v>0.7056441585485556</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2654513462694137</v>
+        <v>0.8024367960652508</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>72933</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>64986</v>
+        <v>638</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>79119</v>
+        <v>5478</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7536098699116881</v>
+        <v>0.02091473841982325</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6714995630281011</v>
+        <v>0.00659377791370222</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.8175339467336639</v>
+        <v>0.05659918362422012</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>70506</v>
+        <v>3356</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>63025</v>
+        <v>1306</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>76937</v>
+        <v>7424</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7559678213478657</v>
+        <v>0.03598653398408653</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6757515495440841</v>
+        <v>0.01400199825949694</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.8249244920415855</v>
+        <v>0.07959805769193443</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>208</v>
+        <v>8</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>143439</v>
+        <v>5380</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>134103</v>
+        <v>2653</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>152498</v>
+        <v>10624</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7547670540836127</v>
+        <v>0.02831134676461657</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7056441585485556</v>
+        <v>0.01395873478471465</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.8024367960652508</v>
+        <v>0.05590243579599176</v>
       </c>
     </row>
     <row r="11">
@@ -3552,213 +3552,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1396</v>
+        <v>21822</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>15877</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4760</v>
+        <v>29277</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.0161888308568663</v>
+        <v>0.2530960636627708</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.1841434814124221</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.05520791789454782</v>
+        <v>0.3395593930391155</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1544</v>
+        <v>24467</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>17816</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5241</v>
+        <v>31665</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01791816426845465</v>
+        <v>0.2839818051071016</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>0.2067829374712055</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.06083529785439912</v>
+        <v>0.3675235671590439</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>2940</v>
+        <v>46289</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>717</v>
+        <v>37253</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>7079</v>
+        <v>55535</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01705317330003623</v>
+        <v>0.2685331430832094</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.004157434288367083</v>
+        <v>0.2161126043805759</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.04106536823117499</v>
+        <v>0.322167092473736</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>21822</v>
+        <v>63004</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>15877</v>
+        <v>55494</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>29277</v>
+        <v>69348</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2530960636627708</v>
+        <v>0.730715105480363</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1841434814124221</v>
+        <v>0.643617321017707</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3395593930391155</v>
+        <v>0.804290309874374</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>24467</v>
+        <v>60146</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>17816</v>
+        <v>52872</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>31665</v>
+        <v>66844</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2839818051071016</v>
+        <v>0.6981000306244438</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2067829374712055</v>
+        <v>0.613669672634531</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3675235671590439</v>
+        <v>0.7758439290717719</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>68</v>
+        <v>178</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>46289</v>
+        <v>123150</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>37253</v>
+        <v>113477</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>55535</v>
+        <v>132135</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2685331430832094</v>
+        <v>0.7144136836167544</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2161126043805759</v>
+        <v>0.6582993110283417</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.322167092473736</v>
+        <v>0.766539738561916</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>63004</v>
+        <v>1396</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>55494</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>69348</v>
+        <v>4760</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.730715105480363</v>
+        <v>0.0161888308568663</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.643617321017707</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.804290309874374</v>
+        <v>0.05520791789454782</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>60146</v>
+        <v>1544</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>52872</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>66844</v>
+        <v>5241</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6981000306244438</v>
+        <v>0.01791816426845465</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.613669672634531</v>
+        <v>0</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7758439290717719</v>
+        <v>0.06083529785439912</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>123150</v>
+        <v>2940</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>113477</v>
+        <v>717</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>132135</v>
+        <v>7079</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7144136836167544</v>
+        <v>0.01705317330003623</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6582993110283417</v>
+        <v>0.004157434288367083</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.766539738561916</v>
+        <v>0.04106536823117499</v>
       </c>
     </row>
     <row r="15">
@@ -3840,213 +3840,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>7815</v>
+        <v>59818</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4081</v>
+        <v>49164</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>14054</v>
+        <v>70861</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.03435990812440565</v>
+        <v>0.2630078399651198</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01794387084104994</v>
+        <v>0.2161661532856046</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.06179169437694368</v>
+        <v>0.3115627833165198</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3372</v>
+        <v>59957</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>731</v>
+        <v>50104</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>7807</v>
+        <v>71003</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01647799345880683</v>
+        <v>0.2929814878729189</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.003569795118473823</v>
+        <v>0.2448333909950065</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03814697727466514</v>
+        <v>0.3469574048762812</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>11187</v>
+        <v>119775</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>6791</v>
+        <v>106284</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>18818</v>
+        <v>135642</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.02589058404084134</v>
+        <v>0.2772041127270164</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.015716620627972</v>
+        <v>0.245980772486593</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.04355184190922358</v>
+        <v>0.3139247364909518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>59818</v>
+        <v>159805</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>49164</v>
+        <v>148079</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>70861</v>
+        <v>171100</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2630078399651198</v>
+        <v>0.7026322519104745</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2161661532856046</v>
+        <v>0.6510731523787966</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3115627833165198</v>
+        <v>0.7522941120756859</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>90</v>
+        <v>203</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>59957</v>
+        <v>141316</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>50104</v>
+        <v>129909</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>71003</v>
+        <v>151944</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2929814878729189</v>
+        <v>0.6905405186682742</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2448333909950065</v>
+        <v>0.6347975064102226</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3469574048762812</v>
+        <v>0.7424699902115345</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>173</v>
+        <v>432</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>119775</v>
+        <v>301121</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>106284</v>
+        <v>283288</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>135642</v>
+        <v>315266</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2772041127270164</v>
+        <v>0.6969053032321423</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.245980772486593</v>
+        <v>0.6556343236355182</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3139247364909518</v>
+        <v>0.7296411204204751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>229</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>159805</v>
+        <v>7815</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>148079</v>
+        <v>4081</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>171100</v>
+        <v>14054</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7026322519104745</v>
+        <v>0.03435990812440565</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6510731523787966</v>
+        <v>0.01794387084104994</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7522941120756859</v>
+        <v>0.06179169437694368</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>141316</v>
+        <v>3372</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>129909</v>
+        <v>731</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>151944</v>
+        <v>7807</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6905405186682742</v>
+        <v>0.01647799345880683</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6347975064102226</v>
+        <v>0.003569795118473823</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7424699902115345</v>
+        <v>0.03814697727466514</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>432</v>
+        <v>15</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>301121</v>
+        <v>11187</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>283288</v>
+        <v>6791</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>315266</v>
+        <v>18818</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.6969053032321423</v>
+        <v>0.02589058404084134</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6556343236355182</v>
+        <v>0.015716620627972</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7296411204204751</v>
+        <v>0.04355184190922358</v>
       </c>
     </row>
     <row r="19">
@@ -4128,213 +4128,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>6398</v>
+        <v>41009</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2982</v>
+        <v>33063</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>11717</v>
+        <v>51245</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.04536046878548541</v>
+        <v>0.2907283874143782</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02114294616877413</v>
+        <v>0.2343948357607228</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.08306430722869861</v>
+        <v>0.3632904959264018</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>6383</v>
+        <v>36129</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3349</v>
+        <v>28652</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>11284</v>
+        <v>46115</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.0427877689055511</v>
+        <v>0.2421995007884761</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.02245432709517315</v>
+        <v>0.1920803131772123</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.07564808716239152</v>
+        <v>0.3091446310820078</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>12781</v>
+        <v>77138</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>8014</v>
+        <v>65598</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>19605</v>
+        <v>90460</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.04403816564044644</v>
+        <v>0.2657857581123127</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02761245438284406</v>
+        <v>0.2260248825205411</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.0675522546439726</v>
+        <v>0.3116880386003504</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>41009</v>
+        <v>93649</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>33063</v>
+        <v>82300</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>51245</v>
+        <v>101941</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2907283874143782</v>
+        <v>0.6639111438001364</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2343948357607228</v>
+        <v>0.5834495298109471</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3632904959264018</v>
+        <v>0.7226968937805294</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>36129</v>
+        <v>106658</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>28652</v>
+        <v>96706</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>46115</v>
+        <v>115129</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2421995007884761</v>
+        <v>0.7150127303059728</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1920803131772123</v>
+        <v>0.6482992054973238</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3091446310820078</v>
+        <v>0.7718048864769937</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>77138</v>
+        <v>200307</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>65598</v>
+        <v>186711</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>90460</v>
+        <v>212801</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2657857581123127</v>
+        <v>0.6901760762472409</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2260248825205411</v>
+        <v>0.6433306863707472</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.3116880386003504</v>
+        <v>0.7332239397353809</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>93649</v>
+        <v>6398</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>82300</v>
+        <v>2982</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>101941</v>
+        <v>11717</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6639111438001364</v>
+        <v>0.04536046878548541</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.5834495298109471</v>
+        <v>0.02114294616877413</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7226968937805294</v>
+        <v>0.08306430722869861</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>106658</v>
+        <v>6383</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>96706</v>
+        <v>3349</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>115129</v>
+        <v>11284</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7150127303059728</v>
+        <v>0.0427877689055511</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6482992054973238</v>
+        <v>0.02245432709517315</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7718048864769937</v>
+        <v>0.07564808716239152</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>279</v>
+        <v>19</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>200307</v>
+        <v>12781</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>186711</v>
+        <v>8014</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>212801</v>
+        <v>19605</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.6901760762472409</v>
+        <v>0.04403816564044644</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6433306863707472</v>
+        <v>0.02761245438284406</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7332239397353809</v>
+        <v>0.0675522546439726</v>
       </c>
     </row>
     <row r="23">
@@ -4416,213 +4416,213 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1389</v>
+        <v>12291</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>7697</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>4886</v>
+        <v>17913</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.0187550789543695</v>
+        <v>0.1660157765298328</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>0.103961861134259</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.06599820619449308</v>
+        <v>0.2419462590605737</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>666</v>
+        <v>13469</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>8437</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>3399</v>
+        <v>18868</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.01236127793843784</v>
+        <v>0.2498294076005648</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>0.156494064984834</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.06305565673809914</v>
+        <v>0.3499756040512358</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>2055</v>
+        <v>25760</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>654</v>
+        <v>19015</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>5538</v>
+        <v>33819</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.01606107187000104</v>
+        <v>0.2013303750462046</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.00510830896124576</v>
+        <v>0.1486134585584262</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.0432814045880426</v>
+        <v>0.2643184917355466</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>12291</v>
+        <v>60358</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>7697</v>
+        <v>54617</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17913</v>
+        <v>65311</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.1660157765298328</v>
+        <v>0.8152291445157976</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.103961861134259</v>
+        <v>0.7376885965754115</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.2419462590605737</v>
+        <v>0.8821221040923668</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>13469</v>
+        <v>39776</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>8437</v>
+        <v>34151</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>18868</v>
+        <v>44818</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2498294076005648</v>
+        <v>0.7378093144609974</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.156494064984834</v>
+        <v>0.6334682871273866</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3499756040512358</v>
+        <v>0.8313343353600424</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>25760</v>
+        <v>100134</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>19015</v>
+        <v>92192</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>33819</v>
+        <v>107029</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.2013303750462046</v>
+        <v>0.7826085530837943</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.1486134585584262</v>
+        <v>0.7205360557473306</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.2643184917355466</v>
+        <v>0.8364990008199258</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>60358</v>
+        <v>1389</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>54617</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>65311</v>
+        <v>4886</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.8152291445157976</v>
+        <v>0.0187550789543695</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.7376885965754115</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.8821221040923668</v>
+        <v>0.06599820619449308</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>39776</v>
+        <v>666</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>34151</v>
+        <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>44818</v>
+        <v>3399</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.7378093144609974</v>
+        <v>0.01236127793843784</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6334682871273866</v>
+        <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8313343353600424</v>
+        <v>0.06305565673809914</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>100134</v>
+        <v>2055</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>92192</v>
+        <v>654</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>107029</v>
+        <v>5538</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.7826085530837943</v>
+        <v>0.01606107187000104</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.7205360557473306</v>
+        <v>0.00510830896124576</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.8364990008199258</v>
+        <v>0.0432814045880426</v>
       </c>
     </row>
     <row r="27">
@@ -4704,213 +4704,213 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>30</v>
+        <v>262</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>21013</v>
+        <v>183428</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>14598</v>
+        <v>164934</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>29951</v>
+        <v>202026</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.02937700744566156</v>
+        <v>0.2564366441181954</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.02040899820971151</v>
+        <v>0.2305807954356461</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.04187252011592786</v>
+        <v>0.2824369633322037</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>16747</v>
+        <v>171514</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>11594</v>
+        <v>152913</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>24829</v>
+        <v>189796</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.02473355753181467</v>
+        <v>0.2533134199951349</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.01712335040416413</v>
+        <v>0.2258413345391593</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.03667060816695086</v>
+        <v>0.2803144516757098</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>54</v>
+        <v>516</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>37760</v>
+        <v>354942</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>27880</v>
+        <v>325990</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>47849</v>
+        <v>384870</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.02711900444930236</v>
+        <v>0.2549178919922939</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.02002328221411834</v>
+        <v>0.2341248264683224</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.03436482715055226</v>
+        <v>0.2764117561495189</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>262</v>
+        <v>729</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>183428</v>
+        <v>510855</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>164934</v>
+        <v>489022</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>202026</v>
+        <v>528612</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.2564366441181954</v>
+        <v>0.714186348436143</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.2305807954356461</v>
+        <v>0.6836623337703684</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.2824369633322037</v>
+        <v>0.7390110135239245</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>171514</v>
+        <v>488821</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>152913</v>
+        <v>470158</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>189796</v>
+        <v>507207</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2533134199951349</v>
+        <v>0.7219530224730504</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2258413345391593</v>
+        <v>0.694387900650426</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2803144516757098</v>
+        <v>0.7491064672827384</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>516</v>
+        <v>1429</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>354942</v>
+        <v>999677</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>325990</v>
+        <v>970684</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>384870</v>
+        <v>1030661</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.2549178919922939</v>
+        <v>0.7179631035584036</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.2341248264683224</v>
+        <v>0.6971409682417511</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.2764117561495189</v>
+        <v>0.740216015902648</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>729</v>
+        <v>30</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>510855</v>
+        <v>21013</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>489022</v>
+        <v>14598</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>528612</v>
+        <v>29951</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.714186348436143</v>
+        <v>0.02937700744566156</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.6836623337703684</v>
+        <v>0.02040899820971151</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.7390110135239245</v>
+        <v>0.04187252011592786</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>700</v>
+        <v>24</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>488821</v>
+        <v>16747</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>470158</v>
+        <v>11594</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>507207</v>
+        <v>24829</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7219530224730504</v>
+        <v>0.02473355753181467</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.694387900650426</v>
+        <v>0.01712335040416413</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.7491064672827384</v>
+        <v>0.03667060816695086</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1429</v>
+        <v>54</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>999677</v>
+        <v>37760</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>970684</v>
+        <v>27880</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>1030661</v>
+        <v>47849</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.7179631035584036</v>
+        <v>0.02711900444930236</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.6971409682417511</v>
+        <v>0.02002328221411834</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.740216015902648</v>
+        <v>0.03436482715055226</v>
       </c>
     </row>
     <row r="31">
@@ -5226,213 +5226,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1236</v>
+        <v>30977</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>23530</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4390</v>
+        <v>38174</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.012385186066571</v>
+        <v>0.3103984776943333</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.2357814295525276</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04399256926408529</v>
+        <v>0.3825198071203131</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2236</v>
+        <v>32748</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>541</v>
+        <v>26077</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>6612</v>
+        <v>40890</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.02732212395295009</v>
+        <v>0.4001998881369468</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.006616696623598449</v>
+        <v>0.3186768799011235</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.0807989274285186</v>
+        <v>0.4997104139509101</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>3472</v>
+        <v>63724</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>1165</v>
+        <v>53647</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>8013</v>
+        <v>75633</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01911479418244286</v>
+        <v>0.3508571249169636</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.006411680112734225</v>
+        <v>0.2953749451239196</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.04411577615415097</v>
+        <v>0.4164213935236961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>30977</v>
+        <v>67584</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23530</v>
+        <v>59977</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>38174</v>
+        <v>74737</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3103984776943333</v>
+        <v>0.6772163362390957</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2357814295525276</v>
+        <v>0.6009885013094889</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3825198071203131</v>
+        <v>0.7488903306281832</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>32748</v>
+        <v>46845</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>26077</v>
+        <v>39695</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>40890</v>
+        <v>53766</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4001998881369468</v>
+        <v>0.5724779879101031</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3186768799011235</v>
+        <v>0.4850982066675134</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4997104139509101</v>
+        <v>0.6570647209537911</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>63724</v>
+        <v>114429</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>53647</v>
+        <v>102815</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>75633</v>
+        <v>124369</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.3508571249169636</v>
+        <v>0.6300280809005936</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2953749451239196</v>
+        <v>0.5660860548127588</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.4164213935236961</v>
+        <v>0.684755519788369</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>67584</v>
+        <v>1236</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>59977</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>74737</v>
+        <v>4390</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6772163362390957</v>
+        <v>0.012385186066571</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6009885013094889</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7488903306281832</v>
+        <v>0.04399256926408529</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>46845</v>
+        <v>2236</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>39695</v>
+        <v>541</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>53766</v>
+        <v>6612</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5724779879101031</v>
+        <v>0.02732212395295009</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4850982066675134</v>
+        <v>0.006616696623598449</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.6570647209537911</v>
+        <v>0.0807989274285186</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>114429</v>
+        <v>3472</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>102815</v>
+        <v>1165</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>124369</v>
+        <v>8013</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6300280809005936</v>
+        <v>0.01911479418244286</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.5660860548127588</v>
+        <v>0.006411680112734225</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.684755519788369</v>
+        <v>0.04411577615415097</v>
       </c>
     </row>
     <row r="7">
@@ -5514,213 +5514,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1971</v>
+        <v>35177</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>639</v>
+        <v>28138</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5246</v>
+        <v>44539</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.017779233821086</v>
+        <v>0.3173013641731343</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.005765193991455133</v>
+        <v>0.2538132706670064</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04731813333047769</v>
+        <v>0.4017519242623164</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1899</v>
+        <v>25482</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>568</v>
+        <v>18598</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>5373</v>
+        <v>33384</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01815488989876187</v>
+        <v>0.243657384535661</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.005428827630945491</v>
+        <v>0.1778338308081309</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.05137764037875907</v>
+        <v>0.3192190395597914</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>3870</v>
+        <v>60658</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1827</v>
+        <v>49793</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>8330</v>
+        <v>72271</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01796158424171294</v>
+        <v>0.2815532119094511</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.008481043706177215</v>
+        <v>0.2311208745976614</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.0386626581497769</v>
+        <v>0.3354530639415316</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>35177</v>
+        <v>73714</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>28138</v>
+        <v>65056</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>44539</v>
+        <v>81359</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3173013641731343</v>
+        <v>0.6649194020057797</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2538132706670064</v>
+        <v>0.5868228674248015</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.4017519242623164</v>
+        <v>0.7338789165556745</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>25482</v>
+        <v>77200</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>18598</v>
+        <v>68945</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>33384</v>
+        <v>84456</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.243657384535661</v>
+        <v>0.7381877255655771</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1778338308081309</v>
+        <v>0.6592605332346104</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3192190395597914</v>
+        <v>0.8075688694972013</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>60658</v>
+        <v>150914</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>49793</v>
+        <v>139007</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>72271</v>
+        <v>162202</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2815532119094511</v>
+        <v>0.7004852038488359</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2311208745976614</v>
+        <v>0.645216418273573</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3354530639415316</v>
+        <v>0.7528815175565146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>73714</v>
+        <v>1971</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>65056</v>
+        <v>639</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>81359</v>
+        <v>5246</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6649194020057797</v>
+        <v>0.017779233821086</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5868228674248015</v>
+        <v>0.005765193991455133</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7338789165556745</v>
+        <v>0.04731813333047769</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>77200</v>
+        <v>1899</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>68945</v>
+        <v>568</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>84456</v>
+        <v>5373</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7381877255655771</v>
+        <v>0.01815488989876187</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6592605332346104</v>
+        <v>0.005428827630945491</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.8075688694972013</v>
+        <v>0.05137764037875907</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>220</v>
+        <v>6</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>150914</v>
+        <v>3870</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>139007</v>
+        <v>1827</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>162202</v>
+        <v>8330</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7004852038488359</v>
+        <v>0.01796158424171294</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.645216418273573</v>
+        <v>0.008481043706177215</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7528815175565146</v>
+        <v>0.0386626581497769</v>
       </c>
     </row>
     <row r="11">
@@ -5802,205 +5802,205 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>646</v>
+        <v>21541</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>15596</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3690</v>
+        <v>28732</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.008845472502446146</v>
+        <v>0.2950711988854919</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.2136431056828849</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.05054429675504214</v>
+        <v>0.3935755861321656</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
+        <v>19862</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>14400</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>26091</v>
+      </c>
       <c r="N12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="6" t="inlineStr"/>
-      <c r="P12" s="6" t="inlineStr"/>
+        <v>0.3211776363749971</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0.2328584668688297</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.4219149364642583</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>646</v>
+        <v>41402</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>0</v>
+        <v>33401</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>3439</v>
+        <v>50383</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.004788832055928153</v>
+        <v>0.3070439261993955</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0</v>
+        <v>0.2477082111306076</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02550671501129269</v>
+        <v>0.373645958395269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>21541</v>
+        <v>50815</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>15596</v>
+        <v>43649</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>28732</v>
+        <v>56770</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2950711988854919</v>
+        <v>0.6960833286120619</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2136431056828849</v>
+        <v>0.5979156442672677</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3935755861321656</v>
+        <v>0.7776438750626913</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>19862</v>
+        <v>41978</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>14400</v>
+        <v>35749</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>26091</v>
+        <v>47440</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3211776363749971</v>
+        <v>0.6788223636250029</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2328584668688297</v>
+        <v>0.5780850635357418</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4219149364642583</v>
+        <v>0.7671415331311703</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>41402</v>
+        <v>92794</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>33401</v>
+        <v>83751</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>50383</v>
+        <v>101134</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3070439261993955</v>
+        <v>0.6881672417446764</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2477082111306076</v>
+        <v>0.6211035194361042</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.373645958395269</v>
+        <v>0.7500216770056624</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>50815</v>
+        <v>646</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>43649</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>56770</v>
+        <v>3690</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6960833286120619</v>
+        <v>0.008845472502446146</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5979156442672677</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7776438750626913</v>
+        <v>0.05054429675504214</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>41978</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>35749</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>47440</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="6" t="n">
-        <v>0.6788223636250029</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>0.5780850635357418</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>0.7671415331311703</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="5" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>92794</v>
+        <v>646</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>83751</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>101134</v>
+        <v>3439</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6881672417446764</v>
+        <v>0.004788832055928153</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6211035194361042</v>
+        <v>0</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7500216770056624</v>
+        <v>0.02550671501129269</v>
       </c>
     </row>
     <row r="15">
@@ -6082,213 +6082,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2750</v>
+        <v>72148</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>676</v>
+        <v>61664</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6135</v>
+        <v>83467</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0131852942381222</v>
+        <v>0.3459318199172733</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.003238946079107366</v>
+        <v>0.2956663514844721</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02941414493067678</v>
+        <v>0.4002026704828779</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5174</v>
+        <v>68749</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2616</v>
+        <v>57358</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>9582</v>
+        <v>79527</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02335343478378407</v>
+        <v>0.3103190927988828</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.01180984483020926</v>
+        <v>0.2589026057176596</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04325107020241022</v>
+        <v>0.3589688035984425</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>13</v>
+        <v>210</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>7924</v>
+        <v>140897</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>4436</v>
+        <v>125351</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>13608</v>
+        <v>157564</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01842281152385352</v>
+        <v>0.3275880260803382</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.01031288956688108</v>
+        <v>0.2914443943776336</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03163809780353988</v>
+        <v>0.3663404351215691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>72148</v>
+        <v>133663</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>61664</v>
+        <v>122819</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>83467</v>
+        <v>144528</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3459318199172733</v>
+        <v>0.6408828858446044</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2956663514844721</v>
+        <v>0.5888882678930065</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4002026704828779</v>
+        <v>0.6929755281344915</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>68749</v>
+        <v>147620</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>57358</v>
+        <v>135749</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>79527</v>
+        <v>158596</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3103190927988828</v>
+        <v>0.6663274724173331</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2589026057176596</v>
+        <v>0.6127442626950153</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3589688035984425</v>
+        <v>0.7158678267923811</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>210</v>
+        <v>412</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>140897</v>
+        <v>281283</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>125351</v>
+        <v>265175</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>157564</v>
+        <v>298099</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.3275880260803382</v>
+        <v>0.6539891623958083</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2914443943776336</v>
+        <v>0.6165366330498232</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3663404351215691</v>
+        <v>0.6930855937195251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>133663</v>
+        <v>2750</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>122819</v>
+        <v>676</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>144528</v>
+        <v>6135</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.6408828858446044</v>
+        <v>0.0131852942381222</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.5888882678930065</v>
+        <v>0.003238946079107366</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.6929755281344915</v>
+        <v>0.02941414493067678</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>223</v>
+        <v>9</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>147620</v>
+        <v>5174</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>135749</v>
+        <v>2616</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>158596</v>
+        <v>9582</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6663274724173331</v>
+        <v>0.02335343478378407</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6127442626950153</v>
+        <v>0.01180984483020926</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7158678267923811</v>
+        <v>0.04325107020241022</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>412</v>
+        <v>13</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>281283</v>
+        <v>7924</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>265175</v>
+        <v>4436</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>298099</v>
+        <v>13608</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.6539891623958083</v>
+        <v>0.01842281152385352</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6165366330498232</v>
+        <v>0.01031288956688108</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.6930855937195251</v>
+        <v>0.03163809780353988</v>
       </c>
     </row>
     <row r="19">
@@ -6370,213 +6370,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1357</v>
+        <v>44149</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>35131</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4929</v>
+        <v>53184</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.009485649046732852</v>
+        <v>0.30854611257634</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0</v>
+        <v>0.2455189101233278</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03444733796521456</v>
+        <v>0.3716900904350194</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1741</v>
+        <v>34582</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>543</v>
+        <v>27059</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4618</v>
+        <v>43174</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01284724166530075</v>
+        <v>0.2552046067525005</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.004004229385942788</v>
+        <v>0.1996876929944748</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03407742030341571</v>
+        <v>0.3186119738163613</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>3098</v>
+        <v>78731</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>1139</v>
+        <v>66415</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>6851</v>
+        <v>91770</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01112070124811641</v>
+        <v>0.282601223823122</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.004086641784009357</v>
+        <v>0.2383927905716405</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.0245915630592602</v>
+        <v>0.3294015542378765</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>44149</v>
+        <v>97581</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>35131</v>
+        <v>88331</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>53184</v>
+        <v>106516</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.30854611257634</v>
+        <v>0.6819682383769272</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2455189101233278</v>
+        <v>0.6173170393423146</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3716900904350194</v>
+        <v>0.7444075168242865</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>34582</v>
+        <v>99183</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>27059</v>
+        <v>90187</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>43174</v>
+        <v>106913</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2552046067525005</v>
+        <v>0.7319481515821987</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1996876929944748</v>
+        <v>0.665557654406575</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3186119738163613</v>
+        <v>0.7889942733308121</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>115</v>
+        <v>283</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>78731</v>
+        <v>196766</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>66415</v>
+        <v>183917</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>91770</v>
+        <v>208917</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.282601223823122</v>
+        <v>0.7062780749287616</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2383927905716405</v>
+        <v>0.6601602738226153</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.3294015542378765</v>
+        <v>0.7498944581985759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>97581</v>
+        <v>1357</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>88331</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>106516</v>
+        <v>4929</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6819682383769272</v>
+        <v>0.009485649046732852</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6173170393423146</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7444075168242865</v>
+        <v>0.03444733796521456</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>99183</v>
+        <v>1741</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>90187</v>
+        <v>543</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>106913</v>
+        <v>4618</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7319481515821987</v>
+        <v>0.01284724166530075</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.665557654406575</v>
+        <v>0.004004229385942788</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7889942733308121</v>
+        <v>0.03407742030341571</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>283</v>
+        <v>5</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>196766</v>
+        <v>3098</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>183917</v>
+        <v>1139</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>208917</v>
+        <v>6851</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7062780749287616</v>
+        <v>0.01112070124811641</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6601602738226153</v>
+        <v>0.004086641784009357</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7498944581985759</v>
+        <v>0.0245915630592602</v>
       </c>
     </row>
     <row r="23">
@@ -6658,213 +6658,213 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3413</v>
+        <v>21413</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1312</v>
+        <v>15112</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>7713</v>
+        <v>27849</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.0503187912938098</v>
+        <v>0.3157111765026095</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01934268143942402</v>
+        <v>0.2228142949781562</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.1137209586183272</v>
+        <v>0.4106023091094825</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>573</v>
+        <v>16588</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>11570</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>2870</v>
+        <v>23132</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.009373124574615158</v>
+        <v>0.271545472423538</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>0.1894017870792285</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.04698277624536736</v>
+        <v>0.3786743521850042</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>3985</v>
+        <v>38001</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>1423</v>
+        <v>30136</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>8392</v>
+        <v>46749</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.03091597936053953</v>
+        <v>0.2947824942070304</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.0110376283388618</v>
+        <v>0.2337748128887526</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.06510168294262023</v>
+        <v>0.3626390007543807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>21413</v>
+        <v>42999</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>15112</v>
+        <v>36060</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>27849</v>
+        <v>48973</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3157111765026095</v>
+        <v>0.6339700322035807</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.2228142949781562</v>
+        <v>0.5316581098868217</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4106023091094825</v>
+        <v>0.722051271794527</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>16588</v>
+        <v>43927</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>11570</v>
+        <v>37651</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>23132</v>
+        <v>49225</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.271545472423538</v>
+        <v>0.7190814030018469</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1894017870792285</v>
+        <v>0.6163439003993574</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3786743521850042</v>
+        <v>0.8058156313077789</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>38001</v>
+        <v>86926</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>30136</v>
+        <v>77903</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>46749</v>
+        <v>94843</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.2947824942070304</v>
+        <v>0.6743015264324301</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.2337748128887526</v>
+        <v>0.6043137807153059</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.3626390007543807</v>
+        <v>0.7357153683615489</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>42999</v>
+        <v>3413</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>36060</v>
+        <v>1312</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>48973</v>
+        <v>7713</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.6339700322035807</v>
+        <v>0.0503187912938098</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5316581098868217</v>
+        <v>0.01934268143942402</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.722051271794527</v>
+        <v>0.1137209586183272</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>43927</v>
+        <v>573</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>37651</v>
+        <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>49225</v>
+        <v>2870</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.7190814030018469</v>
+        <v>0.009373124574615158</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6163439003993574</v>
+        <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8058156313077789</v>
+        <v>0.04698277624536736</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>86926</v>
+        <v>3985</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>77903</v>
+        <v>1423</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>94843</v>
+        <v>8392</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.6743015264324301</v>
+        <v>0.03091597936053953</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.6043137807153059</v>
+        <v>0.0110376283388618</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.7357153683615489</v>
+        <v>0.06510168294262023</v>
       </c>
     </row>
     <row r="27">
@@ -6946,213 +6946,213 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>11373</v>
+        <v>225405</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6586</v>
+        <v>206184</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>17883</v>
+        <v>248024</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01617450967296465</v>
+        <v>0.3205708005719929</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.009366027939472452</v>
+        <v>0.2932349118118738</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.0254334262026026</v>
+        <v>0.3527399672982905</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>11622</v>
+        <v>198010</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>7004</v>
+        <v>179891</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>17867</v>
+        <v>217907</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.01743979110515592</v>
+        <v>0.2971403830894854</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.0105099138817962</v>
+        <v>0.2699507992260374</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.02681159082301085</v>
+        <v>0.326999301012944</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>37</v>
+        <v>627</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>22994</v>
+        <v>423414</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>16425</v>
+        <v>395320</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>31176</v>
+        <v>453107</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.01679017337907426</v>
+        <v>0.3091699712418779</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.01199326084062696</v>
+        <v>0.2886560813184729</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.02276443334886284</v>
+        <v>0.3308514293461623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>325</v>
+        <v>664</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>225405</v>
+        <v>466358</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>206184</v>
+        <v>443686</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>248024</v>
+        <v>485496</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.3205708005719929</v>
+        <v>0.6632546897550424</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.2932349118118738</v>
+        <v>0.6310109185023854</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3527399672982905</v>
+        <v>0.6904726983309663</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>302</v>
+        <v>683</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>198010</v>
+        <v>456753</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>179891</v>
+        <v>436163</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>217907</v>
+        <v>475225</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2971403830894854</v>
+        <v>0.6854198258053587</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2699507992260374</v>
+        <v>0.6545213704137388</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.326999301012944</v>
+        <v>0.7131397914939654</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>627</v>
+        <v>1347</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>423414</v>
+        <v>923110</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>395320</v>
+        <v>894194</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>453107</v>
+        <v>952468</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.3091699712418779</v>
+        <v>0.6740398553790478</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.2886560813184729</v>
+        <v>0.6529255055941091</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.3308514293461623</v>
+        <v>0.6954765053077261</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>664</v>
+        <v>18</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>466358</v>
+        <v>11373</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>443686</v>
+        <v>6586</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>485496</v>
+        <v>17883</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.6632546897550424</v>
+        <v>0.01617450967296465</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.6310109185023854</v>
+        <v>0.009366027939472452</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.6904726983309663</v>
+        <v>0.0254334262026026</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>683</v>
+        <v>19</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>456753</v>
+        <v>11622</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>436163</v>
+        <v>7004</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>475225</v>
+        <v>17867</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.6854198258053587</v>
+        <v>0.01743979110515592</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6545213704137388</v>
+        <v>0.0105099138817962</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.7131397914939654</v>
+        <v>0.02681159082301085</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1347</v>
+        <v>37</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>923110</v>
+        <v>22994</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>894194</v>
+        <v>16425</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>952468</v>
+        <v>31176</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.6740398553790478</v>
+        <v>0.01679017337907426</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.6529255055941091</v>
+        <v>0.01199326084062696</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.6954765053077261</v>
+        <v>0.02276443334886284</v>
       </c>
     </row>
     <row r="31">
@@ -7468,213 +7468,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>979</v>
+        <v>28648</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>21817</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>5069</v>
+        <v>37480</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.00808933951642961</v>
+        <v>0.2368243446548812</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.1803528828511501</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04190310353824925</v>
+        <v>0.3098309393475879</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>874</v>
+        <v>28437</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>21639</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4399</v>
+        <v>35633</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.008555955651339662</v>
+        <v>0.2783480817367094</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>0.2118151869419478</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.04305427454962946</v>
+        <v>0.3487872282356239</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>1853</v>
+        <v>57085</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>0</v>
+        <v>47211</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>6552</v>
+        <v>67687</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.008302983091755036</v>
+        <v>0.2558362882790443</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0</v>
+        <v>0.2115844478179639</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.02936298033424301</v>
+        <v>0.3033496667949139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>28648</v>
+        <v>91342</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21817</v>
+        <v>81980</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>37480</v>
+        <v>98150</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2368243446548812</v>
+        <v>0.7550863158286892</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1803528828511501</v>
+        <v>0.6776922559586317</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3098309393475879</v>
+        <v>0.8113656016698164</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>28437</v>
+        <v>72851</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>21639</v>
+        <v>64773</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>35633</v>
+        <v>79641</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2783480817367094</v>
+        <v>0.7130959626119511</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2118151869419478</v>
+        <v>0.6340202261830692</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3487872282356239</v>
+        <v>0.7795527241050306</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>57085</v>
+        <v>164193</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>47211</v>
+        <v>153215</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>67687</v>
+        <v>174430</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2558362882790443</v>
+        <v>0.7358607286292006</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2115844478179639</v>
+        <v>0.6866594305476292</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3033496667949139</v>
+        <v>0.7817373045121319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>91342</v>
+        <v>979</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>81980</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>98150</v>
+        <v>5069</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7550863158286892</v>
+        <v>0.00808933951642961</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6776922559586317</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.8113656016698164</v>
+        <v>0.04190310353824925</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>72851</v>
+        <v>874</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>64773</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>79641</v>
+        <v>4399</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7130959626119511</v>
+        <v>0.008555955651339662</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6340202261830692</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.7795527241050306</v>
+        <v>0.04305427454962946</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>164193</v>
+        <v>1853</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>153215</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>174430</v>
+        <v>6552</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.7358607286292006</v>
+        <v>0.008302983091755036</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6866594305476292</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7817373045121319</v>
+        <v>0.02936298033424301</v>
       </c>
     </row>
     <row r="7">
@@ -7756,213 +7756,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>863</v>
+        <v>19801</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>14207</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4550</v>
+        <v>27353</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.009444936522355486</v>
+        <v>0.2166408443249273</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>0.1554420066170191</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04978590721958306</v>
+        <v>0.2992766705894311</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2073</v>
+        <v>25057</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>18474</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7181</v>
+        <v>32652</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02147135523218946</v>
+        <v>0.2595344885778339</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>0.1913506660158575</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.07437807765513513</v>
+        <v>0.3381964771800358</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>2936</v>
+        <v>44858</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>854</v>
+        <v>36402</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>8148</v>
+        <v>55220</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01562285494464859</v>
+        <v>0.2386751208142894</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.004543374776435542</v>
+        <v>0.1936872308664362</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.04335516156605174</v>
+        <v>0.2938133766564842</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>19801</v>
+        <v>70734</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>14207</v>
+        <v>62740</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>27353</v>
+        <v>76326</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2166408443249273</v>
+        <v>0.7739142191527175</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1554420066170191</v>
+        <v>0.6864509293002519</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2992766705894311</v>
+        <v>0.835096858813435</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>25057</v>
+        <v>69416</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>18474</v>
+        <v>62145</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>32652</v>
+        <v>76858</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2595344885778339</v>
+        <v>0.7189941561899765</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1913506660158575</v>
+        <v>0.6436870295754997</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3381964771800358</v>
+        <v>0.7960800763249565</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>44858</v>
+        <v>140150</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>36402</v>
+        <v>129382</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>55220</v>
+        <v>148684</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2386751208142894</v>
+        <v>0.7457020242410621</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.1936872308664362</v>
+        <v>0.688407589165696</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2938133766564842</v>
+        <v>0.7911071369710998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>70734</v>
+        <v>863</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>62740</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>76326</v>
+        <v>4550</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7739142191527175</v>
+        <v>0.009444936522355486</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6864509293002519</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.835096858813435</v>
+        <v>0.04978590721958306</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>69416</v>
+        <v>2073</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>62145</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>76858</v>
+        <v>7181</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7189941561899765</v>
+        <v>0.02147135523218946</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6436870295754997</v>
+        <v>0</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7960800763249565</v>
+        <v>0.07437807765513513</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>195</v>
+        <v>3</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>140150</v>
+        <v>2936</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>129382</v>
+        <v>854</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>148684</v>
+        <v>8148</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7457020242410621</v>
+        <v>0.01562285494464859</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.688407589165696</v>
+        <v>0.004543374776435542</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7911071369710998</v>
+        <v>0.04335516156605174</v>
       </c>
     </row>
     <row r="11">
@@ -8044,205 +8044,205 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+        <v>18003</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12723</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>23819</v>
+      </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+        <v>0.3161670417328737</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2234403236132955</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.4183117707407206</v>
+      </c>
       <c r="J12" s="5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>382</v>
+        <v>12870</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>8143</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>2217</v>
+        <v>18833</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.007138157753455267</v>
+        <v>0.2406428273174686</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>0.15226023382854</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04144672988104538</v>
+        <v>0.3521456308078456</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>382</v>
+        <v>30873</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>0</v>
+        <v>23344</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>2471</v>
+        <v>38682</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.003457299507794374</v>
+        <v>0.2795875994813285</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0</v>
+        <v>0.21140945314298</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02237475234183716</v>
+        <v>0.3503090434711086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>18003</v>
+        <v>38938</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>12723</v>
+        <v>33122</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23819</v>
+        <v>44218</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3161670417328737</v>
+        <v>0.6838329582671264</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2234403236132955</v>
+        <v>0.5816882292592793</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4183117707407206</v>
+        <v>0.7765596763867045</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>12870</v>
+        <v>40230</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>8143</v>
+        <v>34080</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>18833</v>
+        <v>44968</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2406428273174686</v>
+        <v>0.7522190149290762</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.15226023382854</v>
+        <v>0.6372285138419261</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3521456308078456</v>
+        <v>0.8408049249177487</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>30873</v>
+        <v>79168</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>23344</v>
+        <v>71428</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>38682</v>
+        <v>86686</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2795875994813285</v>
+        <v>0.7169551010108772</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.21140945314298</v>
+        <v>0.646857071117922</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3503090434711086</v>
+        <v>0.7850353195420187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>38938</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>33122</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>44218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>0.6838329582671264</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>0.5816882292592793</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0.7765596763867045</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>40230</v>
+        <v>382</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>34080</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>44968</v>
+        <v>2217</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7522190149290762</v>
+        <v>0.007138157753455267</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6372285138419261</v>
+        <v>0</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8408049249177487</v>
+        <v>0.04144672988104538</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>79168</v>
+        <v>382</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>71428</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>86686</v>
+        <v>2471</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7169551010108772</v>
+        <v>0.003457299507794374</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.646857071117922</v>
+        <v>0</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7850353195420187</v>
+        <v>0.02237475234183716</v>
       </c>
     </row>
     <row r="15">
@@ -8324,213 +8324,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2605</v>
+        <v>65467</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>53132</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>9665</v>
+        <v>78061</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01291848745449128</v>
+        <v>0.3246644925711834</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>0.2634923946986338</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.04793064262338725</v>
+        <v>0.3871182807909059</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>3310</v>
+        <v>54798</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1180</v>
+        <v>45072</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>7224</v>
+        <v>64925</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.0186719538835252</v>
+        <v>0.3091242766223821</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.006657219866908268</v>
+        <v>0.2542612236447314</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04075228763547074</v>
+        <v>0.3662558820893834</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>5915</v>
+        <v>120265</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>2546</v>
+        <v>105690</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>13812</v>
+        <v>139907</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01561013326612908</v>
+        <v>0.3173943089894289</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.006719532776355744</v>
+        <v>0.2789307488105598</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.0364521279824079</v>
+        <v>0.3692326805733349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>65467</v>
+        <v>133574</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>53132</v>
+        <v>119956</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>78061</v>
+        <v>145724</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3246644925711834</v>
+        <v>0.6624170199743253</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2634923946986338</v>
+        <v>0.5948840919853539</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3871182807909059</v>
+        <v>0.7226715054986379</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>54798</v>
+        <v>119160</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>45072</v>
+        <v>109228</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>64925</v>
+        <v>129301</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3091242766223821</v>
+        <v>0.6722037694940927</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2542612236447314</v>
+        <v>0.6161764205292091</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3662558820893834</v>
+        <v>0.7294135293279599</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>120265</v>
+        <v>252733</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>105690</v>
+        <v>233339</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>139907</v>
+        <v>267961</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.3173943089894289</v>
+        <v>0.666995557744442</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2789307488105598</v>
+        <v>0.6158114472828453</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3692326805733349</v>
+        <v>0.7071845911283658</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>133574</v>
+        <v>2605</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>119956</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>145724</v>
+        <v>9665</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.6624170199743253</v>
+        <v>0.01291848745449128</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.5948840919853539</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7226715054986379</v>
+        <v>0.04793064262338725</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>119160</v>
+        <v>3310</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>109228</v>
+        <v>1180</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>129301</v>
+        <v>7224</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6722037694940927</v>
+        <v>0.0186719538835252</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6161764205292091</v>
+        <v>0.006657219866908268</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7294135293279599</v>
+        <v>0.04075228763547074</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>252733</v>
+        <v>5915</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>233339</v>
+        <v>2546</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>267961</v>
+        <v>13812</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.666995557744442</v>
+        <v>0.01561013326612908</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6158114472828453</v>
+        <v>0.006719532776355744</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7071845911283658</v>
+        <v>0.0364521279824079</v>
       </c>
     </row>
     <row r="19">
@@ -8612,205 +8612,205 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2621</v>
+        <v>38639</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>326</v>
+        <v>28829</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>9892</v>
+        <v>49520</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01768271285358123</v>
+        <v>0.2606489707445881</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.002198438879005013</v>
+        <v>0.1944692847824906</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.06672760610724152</v>
+        <v>0.3340461908255576</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
+        <v>32386</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>25380</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>40610</v>
+      </c>
       <c r="N20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="6" t="inlineStr"/>
-      <c r="P20" s="6" t="inlineStr"/>
+        <v>0.2774770700075047</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0.2174496185210757</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.3479412828860053</v>
+      </c>
       <c r="Q20" s="5" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>2621</v>
+        <v>71025</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>311</v>
+        <v>57583</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>10203</v>
+        <v>84724</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.009893403823728514</v>
+        <v>0.2680618189104365</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.001173954851146534</v>
+        <v>0.2173270520377163</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.03850846088774293</v>
+        <v>0.319762158622484</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>38639</v>
+        <v>106982</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>28829</v>
+        <v>95389</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>49520</v>
+        <v>116779</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2606489707445881</v>
+        <v>0.7216683164018306</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1944692847824906</v>
+        <v>0.6434662809760056</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3340461908255576</v>
+        <v>0.7877524093503984</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>32386</v>
+        <v>84329</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>25380</v>
+        <v>76105</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>40610</v>
+        <v>91335</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2774770700075047</v>
+        <v>0.7225229299924953</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2174496185210757</v>
+        <v>0.6520587171139947</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3479412828860053</v>
+        <v>0.7825503814789242</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>117</v>
+        <v>256</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>71025</v>
+        <v>191312</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>57583</v>
+        <v>177216</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>84724</v>
+        <v>204918</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2680618189104365</v>
+        <v>0.7220447772658348</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2173270520377163</v>
+        <v>0.6688451414445866</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.319762158622484</v>
+        <v>0.7733999276689288</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>106982</v>
+        <v>2621</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>95389</v>
+        <v>326</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>116779</v>
+        <v>9892</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7216683164018306</v>
+        <v>0.01768271285358123</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6434662809760056</v>
+        <v>0.002198438879005013</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7877524093503984</v>
+        <v>0.06672760610724152</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>84329</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>76105</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>91335</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="6" t="n">
-        <v>0.7225229299924953</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>0.6520587171139947</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0.7825503814789242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="5" t="n">
-        <v>256</v>
+        <v>3</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>191312</v>
+        <v>2621</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>177216</v>
+        <v>311</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>204918</v>
+        <v>10203</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7220447772658348</v>
+        <v>0.009893403823728514</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6688451414445866</v>
+        <v>0.001173954851146534</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7733999276689288</v>
+        <v>0.03850846088774293</v>
       </c>
     </row>
     <row r="23">
@@ -8892,213 +8892,213 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>424</v>
+        <v>21131</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>15354</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1965</v>
+        <v>28567</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.00620653402747456</v>
+        <v>0.3094443213995908</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>0.2248442838165542</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.0287728548805372</v>
+        <v>0.4183364816848161</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2524</v>
+        <v>14836</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>750</v>
+        <v>9940</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>6678</v>
+        <v>21358</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.0364565144848177</v>
+        <v>0.2142589226038926</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.01083623505791077</v>
+        <v>0.143543752142178</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.09644446098890176</v>
+        <v>0.3084519109783633</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>2948</v>
+        <v>35967</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>823</v>
+        <v>28110</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>7685</v>
+        <v>44212</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.0214367372113513</v>
+        <v>0.2615205560986148</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.005983373035452924</v>
+        <v>0.2043885743855635</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.05588103594583132</v>
+        <v>0.3214665134853272</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>21131</v>
+        <v>46732</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>15354</v>
+        <v>39383</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>28567</v>
+        <v>52359</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3094443213995908</v>
+        <v>0.6843491445729347</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.2248442838165542</v>
+        <v>0.5767215359138941</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4183364816848161</v>
+        <v>0.7667508773270763</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>14836</v>
+        <v>51883</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>9940</v>
+        <v>44506</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>21358</v>
+        <v>57078</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2142589226038926</v>
+        <v>0.7492845629112898</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.143543752142178</v>
+        <v>0.6427465267862599</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3084519109783633</v>
+        <v>0.8242959280567581</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>35967</v>
+        <v>98616</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>28110</v>
+        <v>90525</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>44212</v>
+        <v>106967</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.2615205560986148</v>
+        <v>0.7170427066900337</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.2043885743855635</v>
+        <v>0.6582149894558685</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.3214665134853272</v>
+        <v>0.7777665065623069</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46732</v>
+        <v>424</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>39383</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>52359</v>
+        <v>1965</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.6843491445729347</v>
+        <v>0.00620653402747456</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5767215359138941</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.7667508773270763</v>
+        <v>0.0287728548805372</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>51883</v>
+        <v>2524</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>44506</v>
+        <v>750</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>57078</v>
+        <v>6678</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.7492845629112898</v>
+        <v>0.0364565144848177</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6427465267862599</v>
+        <v>0.01083623505791077</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8242959280567581</v>
+        <v>0.09644446098890176</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>98616</v>
+        <v>2948</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>90525</v>
+        <v>823</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>106967</v>
+        <v>7685</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.7170427066900337</v>
+        <v>0.0214367372113513</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.6582149894558685</v>
+        <v>0.005983373035452924</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.7777665065623069</v>
+        <v>0.05588103594583132</v>
       </c>
     </row>
     <row r="27">
@@ -9180,213 +9180,213 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>7492</v>
+        <v>191689</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3599</v>
+        <v>170518</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>15965</v>
+        <v>215566</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01089761529319202</v>
+        <v>0.2788276213452991</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.005235482511142734</v>
+        <v>0.248032606790632</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.02322166638641855</v>
+        <v>0.3135578632460699</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>9163</v>
+        <v>168383</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4578</v>
+        <v>151713</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>15715</v>
+        <v>188506</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.01488934279613797</v>
+        <v>0.2736085386785098</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.007438100191936992</v>
+        <v>0.2465206090138771</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.02553545517556346</v>
+        <v>0.3063065808922373</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>20</v>
+        <v>593</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>16655</v>
+        <v>360072</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>10333</v>
+        <v>327820</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>28471</v>
+        <v>386840</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.01278308208102519</v>
+        <v>0.2763624212473654</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.007931044402611442</v>
+        <v>0.2516077984426123</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.021851817241661</v>
+        <v>0.2969070408336902</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>307</v>
+        <v>642</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>191689</v>
+        <v>488302</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>170518</v>
+        <v>464917</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>215566</v>
+        <v>510948</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.2788276213452991</v>
+        <v>0.710274763361509</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.248032606790632</v>
+        <v>0.6762595541102024</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.3135578632460699</v>
+        <v>0.7432156963452404</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>286</v>
+        <v>623</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>168383</v>
+        <v>437870</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>151713</v>
+        <v>418464</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>188506</v>
+        <v>455842</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2736085386785098</v>
+        <v>0.7115021185253524</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2465206090138771</v>
+        <v>0.6799690918196706</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3063065808922373</v>
+        <v>0.740706194428208</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>593</v>
+        <v>1265</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>360072</v>
+        <v>926172</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>327820</v>
+        <v>898414</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>386840</v>
+        <v>958580</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.2763624212473654</v>
+        <v>0.7108544966716094</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.2516077984426123</v>
+        <v>0.6895500132530672</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.2969070408336902</v>
+        <v>0.7357284323004577</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>642</v>
+        <v>8</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>488302</v>
+        <v>7492</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>464917</v>
+        <v>3599</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>510948</v>
+        <v>15965</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.710274763361509</v>
+        <v>0.01089761529319202</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.6762595541102024</v>
+        <v>0.005235482511142734</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.7432156963452404</v>
+        <v>0.02322166638641855</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>623</v>
+        <v>12</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>437870</v>
+        <v>9163</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>418464</v>
+        <v>4578</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>455842</v>
+        <v>15715</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7115021185253524</v>
+        <v>0.01488934279613797</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6799690918196706</v>
+        <v>0.007438100191936992</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.740706194428208</v>
+        <v>0.02553545517556346</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1265</v>
+        <v>20</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>926172</v>
+        <v>16655</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>898414</v>
+        <v>10333</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>958580</v>
+        <v>28471</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.7108544966716094</v>
+        <v>0.01278308208102519</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.6895500132530672</v>
+        <v>0.007931044402611442</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.7357284323004577</v>
+        <v>0.021851817241661</v>
       </c>
     </row>
     <row r="31">
